--- a/data/gravel/Salsa Stormchaser 2025.xlsx
+++ b/data/gravel/Salsa Stormchaser 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7660C23C-262D-B448-BCBA-2D0A50B5F37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794586E2-501F-6846-9B12-483F57F2A478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2400" yWindow="600" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -2116,9 +2116,7 @@
       <c r="A45" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">

--- a/data/gravel/Salsa Stormchaser 2025.xlsx
+++ b/data/gravel/Salsa Stormchaser 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794586E2-501F-6846-9B12-483F57F2A478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9B6537-300D-2D48-B7A2-2C78C77E5DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2400" yWindow="600" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -278,9 +278,6 @@
     <t>Stormchaser</t>
   </si>
   <si>
-    <t>https://www.salsacycles.com/products/2021_stormchaser_frameset</t>
-  </si>
-  <si>
     <t>H. Seat Tube Angle</t>
   </si>
   <si>
@@ -414,6 +411,12 @@
   </si>
   <si>
     <t>a8:i33</t>
+  </si>
+  <si>
+    <t>https://www.salsacycles.com/collections/stormchaser</t>
+  </si>
+  <si>
+    <t>https://www.salsacycles.com/cdn/shop/files/salsa-stormchaser-apex-eagle-sus-berry-BK00382-1920x1080-uc-1.png?v=1737048511&amp;width=1445</t>
   </si>
 </sst>
 </file>
@@ -824,7 +827,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -832,7 +840,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
@@ -840,52 +848,52 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="M8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -893,7 +901,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" s="6">
         <v>506</v>
@@ -917,7 +925,7 @@
         <v>605</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N9" s="4">
         <v>506</v>
@@ -946,7 +954,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" s="6">
         <v>686</v>
@@ -970,7 +978,7 @@
         <v>843</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N10" s="4">
         <v>686</v>
@@ -999,7 +1007,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11" s="6">
         <v>366</v>
@@ -1023,7 +1031,7 @@
         <v>411</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N11" s="4">
         <v>366</v>
@@ -1052,7 +1060,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="6">
         <v>530</v>
@@ -1076,7 +1084,7 @@
         <v>637</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N12" s="4">
         <v>530</v>
@@ -1105,7 +1113,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="6">
         <v>390</v>
@@ -1129,7 +1137,7 @@
         <v>570</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N13" s="4">
         <v>390</v>
@@ -1158,7 +1166,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="6">
         <v>90</v>
@@ -1182,7 +1190,7 @@
         <v>205</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N14" s="4">
         <v>90</v>
@@ -1211,7 +1219,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C15" s="6">
         <v>70</v>
@@ -1235,7 +1243,7 @@
         <v>70</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N15" s="4">
         <v>70</v>
@@ -1264,7 +1272,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" s="6">
         <v>75.25</v>
@@ -1288,7 +1296,7 @@
         <v>73.099999999999994</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N16" s="4">
         <v>75.25</v>
@@ -1317,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" s="6">
         <v>70</v>
@@ -1341,7 +1349,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N17" s="4">
         <v>70</v>
@@ -1367,10 +1375,10 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C18" s="6">
         <v>290</v>
@@ -1394,7 +1402,7 @@
         <v>290</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N18" s="4">
         <v>290</v>
@@ -1423,7 +1431,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="6">
         <v>435</v>
@@ -1447,28 +1455,28 @@
         <v>435</v>
       </c>
       <c r="M19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N19" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="N19" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="O19" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
@@ -1476,7 +1484,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C20" s="6">
         <v>420</v>
@@ -1500,7 +1508,7 @@
         <v>420</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N20" s="4">
         <v>420</v>
@@ -1529,7 +1537,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21" s="6">
         <v>51</v>
@@ -1553,7 +1561,7 @@
         <v>51</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N21" s="4">
         <v>51</v>
@@ -1582,7 +1590,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" s="6">
         <v>1017</v>
@@ -1606,28 +1614,28 @@
         <v>1101</v>
       </c>
       <c r="M22" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="O22" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="P22" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="Q22" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="R22" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="S22" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="S22" s="4" t="s">
+      <c r="T22" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="T22" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
@@ -1635,7 +1643,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C23" s="6">
         <v>165</v>
@@ -1659,7 +1667,7 @@
         <v>180</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N23" s="4">
         <v>165</v>
@@ -1688,7 +1696,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C24" s="6">
         <v>40</v>
@@ -1712,7 +1720,7 @@
         <v>52</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N24" s="4">
         <v>40</v>
@@ -1741,7 +1749,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C25" s="6">
         <v>60</v>
@@ -1765,7 +1773,7 @@
         <v>110</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N25" s="4">
         <v>60</v>
@@ -1956,7 +1964,7 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C32">
         <v>142</v>
@@ -1982,7 +1990,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C33">
         <v>157</v>
@@ -2008,28 +2016,28 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="E34" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="I34" s="6">
         <v>190</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -2069,7 +2077,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">

--- a/data/gravel/Salsa Stormchaser 2025.xlsx
+++ b/data/gravel/Salsa Stormchaser 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9B6537-300D-2D48-B7A2-2C78C77E5DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FC4127-AC44-7A45-869F-889C521D19DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2400" yWindow="600" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -269,9 +269,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Salsa</t>
   </si>
   <si>
@@ -417,6 +414,15 @@
   </si>
   <si>
     <t>https://www.salsacycles.com/cdn/shop/files/salsa-stormchaser-apex-eagle-sus-berry-BK00382-1920x1080-uc-1.png?v=1737048511&amp;width=1445</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bloomington, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -783,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T73"/>
+  <dimension ref="A1:T74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -795,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -803,7 +809,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -827,12 +833,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -840,7 +846,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
@@ -848,52 +854,52 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="M8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -901,7 +907,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C9" s="6">
         <v>506</v>
@@ -925,7 +931,7 @@
         <v>605</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N9" s="4">
         <v>506</v>
@@ -954,7 +960,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="6">
         <v>686</v>
@@ -978,7 +984,7 @@
         <v>843</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N10" s="4">
         <v>686</v>
@@ -1007,7 +1013,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="6">
         <v>366</v>
@@ -1031,7 +1037,7 @@
         <v>411</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N11" s="4">
         <v>366</v>
@@ -1060,7 +1066,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="6">
         <v>530</v>
@@ -1084,7 +1090,7 @@
         <v>637</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N12" s="4">
         <v>530</v>
@@ -1113,7 +1119,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="6">
         <v>390</v>
@@ -1137,7 +1143,7 @@
         <v>570</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N13" s="4">
         <v>390</v>
@@ -1166,7 +1172,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="6">
         <v>90</v>
@@ -1190,7 +1196,7 @@
         <v>205</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N14" s="4">
         <v>90</v>
@@ -1219,7 +1225,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="6">
         <v>70</v>
@@ -1243,7 +1249,7 @@
         <v>70</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N15" s="4">
         <v>70</v>
@@ -1272,7 +1278,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" s="6">
         <v>75.25</v>
@@ -1296,7 +1302,7 @@
         <v>73.099999999999994</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N16" s="4">
         <v>75.25</v>
@@ -1325,7 +1331,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="6">
         <v>70</v>
@@ -1349,7 +1355,7 @@
         <v>70</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N17" s="4">
         <v>70</v>
@@ -1375,10 +1381,10 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" s="6">
         <v>290</v>
@@ -1402,7 +1408,7 @@
         <v>290</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N18" s="4">
         <v>290</v>
@@ -1431,7 +1437,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="6">
         <v>435</v>
@@ -1455,28 +1461,28 @@
         <v>435</v>
       </c>
       <c r="M19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="N19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="N19" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="O19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
@@ -1484,7 +1490,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" s="6">
         <v>420</v>
@@ -1508,7 +1514,7 @@
         <v>420</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N20" s="4">
         <v>420</v>
@@ -1537,7 +1543,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" s="6">
         <v>51</v>
@@ -1561,7 +1567,7 @@
         <v>51</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N21" s="4">
         <v>51</v>
@@ -1590,7 +1596,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="6">
         <v>1017</v>
@@ -1614,28 +1620,28 @@
         <v>1101</v>
       </c>
       <c r="M22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N22" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="O22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="P22" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="Q22" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="R22" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="S22" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="S22" s="4" t="s">
+      <c r="T22" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="T22" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
@@ -1643,7 +1649,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" s="6">
         <v>165</v>
@@ -1667,7 +1673,7 @@
         <v>180</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N23" s="4">
         <v>165</v>
@@ -1696,7 +1702,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C24" s="6">
         <v>40</v>
@@ -1720,7 +1726,7 @@
         <v>52</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N24" s="4">
         <v>40</v>
@@ -1749,7 +1755,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C25" s="6">
         <v>60</v>
@@ -1773,7 +1779,7 @@
         <v>110</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N25" s="4">
         <v>60</v>
@@ -1964,7 +1970,7 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C32">
         <v>142</v>
@@ -1990,7 +1996,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C33">
         <v>157</v>
@@ -2016,28 +2022,28 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C34" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="E34" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I34" s="6">
         <v>190</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -2077,7 +2083,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -2323,7 +2329,15 @@
         <v>67</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>78</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>127</v>
+      </c>
+      <c r="B74" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Salsa Stormchaser 2025.xlsx
+++ b/data/gravel/Salsa Stormchaser 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FC4127-AC44-7A45-869F-889C521D19DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B124E7-E4B9-AC43-84FB-85241FCB48F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2400" yWindow="600" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="136">
   <si>
     <t>brand</t>
   </si>
@@ -423,6 +423,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -789,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2160,183 +2178,213 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54">
-        <v>38</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>76</v>
+        <v>48</v>
+      </c>
+      <c r="B60">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B62">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>74</v>
+        <v>57</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70">
-        <v>1349</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71">
-        <v>3199</v>
+        <v>59</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>127</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>128</v>
       </c>
     </row>
